--- a/data/trans_orig/P05A03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A03-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2007</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2007 (tasa de respuesta: 99,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>825849</t>
+          <t>822909</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>872063</t>
+          <t>874969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1057608</t>
+          <t>1056523</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1113269</t>
+          <t>1109081</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1893144</t>
+          <t>1898840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1971250</t>
+          <t>1969371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130294</t>
+          <t>132139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175247</t>
+          <t>180434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>168112</t>
+          <t>171484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>222142</t>
+          <t>223215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>316738</t>
+          <t>315921</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>385783</t>
+          <t>383163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34754</t>
+          <t>36192</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19777</t>
+          <t>21073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41268</t>
+          <t>42719</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41218</t>
+          <t>41781</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69739</t>
+          <t>71066</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1367486</t>
+          <t>1366163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1427522</t>
+          <t>1427877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1268230</t>
+          <t>1266293</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1328753</t>
+          <t>1328277</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2652191</t>
+          <t>2648539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2735566</t>
+          <t>2739371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,06%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>206809</t>
+          <t>207719</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>264568</t>
+          <t>265141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>199431</t>
+          <t>200634</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255860</t>
+          <t>255502</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>424609</t>
+          <t>427859</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>503871</t>
+          <t>508424</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34119</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62110</t>
+          <t>62181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40571</t>
+          <t>39759</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68978</t>
+          <t>69743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82223</t>
+          <t>81009</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120513</t>
+          <t>121514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415890</t>
+          <t>415522</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>452358</t>
+          <t>454045</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>354676</t>
+          <t>355500</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>390709</t>
+          <t>392187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>782327</t>
+          <t>784246</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835850</t>
+          <t>836953</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72846</t>
+          <t>71257</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105964</t>
+          <t>106478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67109</t>
+          <t>67427</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101243</t>
+          <t>101869</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147922</t>
+          <t>147521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>197981</t>
+          <t>196026</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11947</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30284</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>23401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47006</t>
+          <t>48582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2642423</t>
+          <t>2646875</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2726713</t>
+          <t>2730191</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2707237</t>
+          <t>2709781</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2801468</t>
+          <t>2799803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5378735</t>
+          <t>5381129</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5504669</t>
+          <t>5509040</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>436667</t>
+          <t>436005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>515588</t>
+          <t>513509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>466910</t>
+          <t>466603</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>553420</t>
+          <t>550222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>926341</t>
+          <t>917937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1042746</t>
+          <t>1033918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72138</t>
+          <t>71632</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109152</t>
+          <t>110735</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76243</t>
+          <t>79545</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>118135</t>
+          <t>118849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>161323</t>
+          <t>165470</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>214393</t>
+          <t>216873</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2012</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2012 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>853856</t>
+          <t>853104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>893184</t>
+          <t>891389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1152486</t>
+          <t>1150165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1196547</t>
+          <t>1196438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2014741</t>
+          <t>2016663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2076936</t>
+          <t>2078948</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58694</t>
+          <t>59668</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93816</t>
+          <t>95280</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99192</t>
+          <t>98716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139090</t>
+          <t>141857</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168363</t>
+          <t>166413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224992</t>
+          <t>222923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15037</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33675</t>
+          <t>32713</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>16656</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37155</t>
+          <t>37329</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35431</t>
+          <t>35114</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65058</t>
+          <t>63552</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1651124</t>
+          <t>1649823</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1716221</t>
+          <t>1716226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,47 +3259,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>84,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1502447</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1472718</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1527143</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>86,54%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>84,83%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1502447</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1469566</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1533731</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,54%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>84,65%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3144282</t>
+          <t>3144760</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3231272</t>
+          <t>3228324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,67%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>188367</t>
+          <t>190143</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>246945</t>
+          <t>249610</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>166868</t>
+          <t>171688</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>226387</t>
+          <t>223642</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>376942</t>
+          <t>378205</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>456988</t>
+          <t>455586</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57455</t>
+          <t>58304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25690</t>
+          <t>25895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51949</t>
+          <t>51901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60840</t>
+          <t>60754</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97421</t>
+          <t>97540</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>395572</t>
+          <t>396927</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>427744</t>
+          <t>428385</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>371201</t>
+          <t>370041</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>404207</t>
+          <t>402305</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>778469</t>
+          <t>779798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>823154</t>
+          <t>823581</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34538</t>
+          <t>35104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62560</t>
+          <t>61897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>40002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69927</t>
+          <t>69839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81783</t>
+          <t>80714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121712</t>
+          <t>121743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27140</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17588</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40774</t>
+          <t>37629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2932358</t>
+          <t>2935870</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3014129</t>
+          <t>3016816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3023315</t>
+          <t>3023544</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3103768</t>
+          <t>3106847</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5984024</t>
+          <t>5982168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6096407</t>
+          <t>6097573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>301478</t>
+          <t>302005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>378048</t>
+          <t>377670</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>330292</t>
+          <t>329850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>402583</t>
+          <t>403335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>657668</t>
+          <t>658119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>759641</t>
+          <t>763547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61186</t>
+          <t>59838</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>97203</t>
+          <t>99160</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57754</t>
+          <t>56359</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91579</t>
+          <t>94237</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,47 +4432,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>152327</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>128670</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>180418</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>2,61%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>152327</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>128541</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>179226</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2016</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2016 (tasa de respuesta: 99,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>627388</t>
+          <t>629074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>663798</t>
+          <t>664609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>809547</t>
+          <t>806515</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>856348</t>
+          <t>854859</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1447993</t>
+          <t>1452829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1509859</t>
+          <t>1514052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60324</t>
+          <t>59701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91767</t>
+          <t>90577</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94925</t>
+          <t>93448</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135625</t>
+          <t>137029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161878</t>
+          <t>160891</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>216311</t>
+          <t>214161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40007</t>
+          <t>39540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27844</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53359</t>
+          <t>54703</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50735</t>
+          <t>49421</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84862</t>
+          <t>83309</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1712582</t>
+          <t>1708155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1778404</t>
+          <t>1777229</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1614686</t>
+          <t>1611293</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1675604</t>
+          <t>1679162</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3342920</t>
+          <t>3346310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3434874</t>
+          <t>3440141</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>224341</t>
+          <t>224233</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>285664</t>
+          <t>287352</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>222114</t>
+          <t>221228</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>277173</t>
+          <t>281901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>463275</t>
+          <t>457934</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>548941</t>
+          <t>544729</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48031</t>
+          <t>48376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80680</t>
+          <t>80742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61615</t>
+          <t>59713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95485</t>
+          <t>95515</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118971</t>
+          <t>116858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167490</t>
+          <t>164042</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>424500</t>
+          <t>424080</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>462448</t>
+          <t>461734</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>437314</t>
+          <t>433617</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>470832</t>
+          <t>469617</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>871226</t>
+          <t>871707</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>921891</t>
+          <t>924012</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60413</t>
+          <t>59882</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92180</t>
+          <t>94836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53581</t>
+          <t>55147</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85218</t>
+          <t>88317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123196</t>
+          <t>123954</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169499</t>
+          <t>168055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31665</t>
+          <t>31260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>12572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31670</t>
+          <t>30913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26099</t>
+          <t>26974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53234</t>
+          <t>52735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2788940</t>
+          <t>2792523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2874889</t>
+          <t>2879354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2885844</t>
+          <t>2886148</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2975672</t>
+          <t>2977881</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5703027</t>
+          <t>5713574</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5832601</t>
+          <t>5833250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>366451</t>
+          <t>364580</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>443910</t>
+          <t>443000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>388374</t>
+          <t>392915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>473461</t>
+          <t>478849</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>784914</t>
+          <t>779443</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>896473</t>
+          <t>888987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89954</t>
+          <t>88670</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>132075</t>
+          <t>132185</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>114644</t>
+          <t>113956</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162049</t>
+          <t>161536</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>215106</t>
+          <t>216089</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>280791</t>
+          <t>279842</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2023</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2023 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>452204</t>
+          <t>452750</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>475806</t>
+          <t>475933</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>655593</t>
+          <t>655528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>681443</t>
+          <t>681361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1114421</t>
+          <t>1117664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1149586</t>
+          <t>1151348</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20446</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40013</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47224</t>
+          <t>47689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71721</t>
+          <t>72373</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73591</t>
+          <t>73105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104340</t>
+          <t>103334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>9533</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24149</t>
+          <t>26038</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10720</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22160</t>
+          <t>22101</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23165</t>
+          <t>23543</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41877</t>
+          <t>42893</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2079074</t>
+          <t>2076547</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2167209</t>
+          <t>2168237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2027777</t>
+          <t>2028598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2111486</t>
+          <t>2109602</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4124045</t>
+          <t>4122569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4249327</t>
+          <t>4239346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95101</t>
+          <t>95566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>169937</t>
+          <t>170979</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95358</t>
+          <t>96813</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>163529</t>
+          <t>162909</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>214962</t>
+          <t>218423</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>317221</t>
+          <t>316798</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48990</t>
+          <t>48834</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25260</t>
+          <t>25247</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51759</t>
+          <t>52440</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47128</t>
+          <t>48201</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91317</t>
+          <t>92651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>553069</t>
+          <t>553850</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>588373</t>
+          <t>587568</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>555987</t>
+          <t>555445</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>584833</t>
+          <t>584543</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1117941</t>
+          <t>1118569</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1164722</t>
+          <t>1165146</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39013</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68062</t>
+          <t>68963</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53196</t>
+          <t>53718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77862</t>
+          <t>80121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98479</t>
+          <t>98933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138281</t>
+          <t>138147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11572</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29708</t>
+          <t>29338</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28535</t>
+          <t>28239</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53861</t>
+          <t>52582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3111640</t>
+          <t>3107834</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3218157</t>
+          <t>3214570</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3255912</t>
+          <t>3260740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3352836</t>
+          <t>3364211</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6389794</t>
+          <t>6392597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6536229</t>
+          <t>6538881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171340</t>
+          <t>173293</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>257408</t>
+          <t>256734</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>214658</t>
+          <t>209987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>296782</t>
+          <t>290877</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>416813</t>
+          <t>407039</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>529733</t>
+          <t>527957</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44571</t>
+          <t>44159</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84041</t>
+          <t>86121</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55344</t>
+          <t>57725</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90208</t>
+          <t>91995</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>110844</t>
+          <t>114172</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>169778</t>
+          <t>164476</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A03-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>822909</t>
+          <t>824406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>874969</t>
+          <t>872530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1056523</t>
+          <t>1052101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1109081</t>
+          <t>1108659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1898840</t>
+          <t>1895442</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1969371</t>
+          <t>1969214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132139</t>
+          <t>130609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180434</t>
+          <t>177286</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>171484</t>
+          <t>173735</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223215</t>
+          <t>226342</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>315921</t>
+          <t>316507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>383163</t>
+          <t>382956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36192</t>
+          <t>35491</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21073</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42719</t>
+          <t>42287</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41781</t>
+          <t>41779</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71066</t>
+          <t>72028</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1366163</t>
+          <t>1368558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1427877</t>
+          <t>1431125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1266293</t>
+          <t>1267336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1328277</t>
+          <t>1330220</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2648539</t>
+          <t>2650899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2739371</t>
+          <t>2740363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>207719</t>
+          <t>206544</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>265141</t>
+          <t>264248</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200634</t>
+          <t>199262</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255502</t>
+          <t>256098</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>427859</t>
+          <t>423175</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>508424</t>
+          <t>504864</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34452</t>
+          <t>33847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62181</t>
+          <t>59634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,82 +1430,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>53577</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>40396</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>69519</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>99390</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>81816</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>120492</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>3,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>53577</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>39759</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>69743</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>99390</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>81009</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>121514</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415522</t>
+          <t>413896</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>454045</t>
+          <t>452845</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>355500</t>
+          <t>357702</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>392187</t>
+          <t>393960</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>784246</t>
+          <t>783275</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>836953</t>
+          <t>835566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71257</t>
+          <t>71467</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106478</t>
+          <t>108125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67427</t>
+          <t>65737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101869</t>
+          <t>99624</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147521</t>
+          <t>147863</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>196026</t>
+          <t>198434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>31013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>23563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22880</t>
+          <t>23571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48582</t>
+          <t>46770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2646875</t>
+          <t>2639528</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2730191</t>
+          <t>2724742</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2709781</t>
+          <t>2711913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2799803</t>
+          <t>2804819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5381129</t>
+          <t>5379320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5509040</t>
+          <t>5502081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>436005</t>
+          <t>437144</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>513509</t>
+          <t>518706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>466603</t>
+          <t>463855</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>550222</t>
+          <t>549148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>917937</t>
+          <t>930705</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1033918</t>
+          <t>1042153</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71632</t>
+          <t>72280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110735</t>
+          <t>111409</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79545</t>
+          <t>80468</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>118849</t>
+          <t>119162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>165470</t>
+          <t>161586</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>216873</t>
+          <t>216013</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>853104</t>
+          <t>853696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>891389</t>
+          <t>892763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1150165</t>
+          <t>1149052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1196438</t>
+          <t>1194945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2016663</t>
+          <t>2015942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2078948</t>
+          <t>2077001</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59668</t>
+          <t>57973</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95280</t>
+          <t>94410</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98716</t>
+          <t>100444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141857</t>
+          <t>142710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166413</t>
+          <t>170163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>222923</t>
+          <t>225490</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32713</t>
+          <t>32842</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16656</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37329</t>
+          <t>36576</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35114</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63552</t>
+          <t>63454</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1649823</t>
+          <t>1653855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1716226</t>
+          <t>1719128</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1472718</t>
+          <t>1471574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1527143</t>
+          <t>1531141</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3144760</t>
+          <t>3147537</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3228324</t>
+          <t>3236404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>190143</t>
+          <t>189668</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>249610</t>
+          <t>248360</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>171688</t>
+          <t>169751</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>223642</t>
+          <t>225091</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>378205</t>
+          <t>374292</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>455586</t>
+          <t>454345</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>27631</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58304</t>
+          <t>56905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25895</t>
+          <t>25997</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51901</t>
+          <t>51925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60754</t>
+          <t>58808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97540</t>
+          <t>98197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>396927</t>
+          <t>396404</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>428385</t>
+          <t>429408</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>370041</t>
+          <t>370637</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>402305</t>
+          <t>403325</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>779798</t>
+          <t>774254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>823581</t>
+          <t>823819</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,66%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35104</t>
+          <t>35016</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61897</t>
+          <t>63243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40002</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69839</t>
+          <t>68718</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80714</t>
+          <t>80566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121743</t>
+          <t>125027</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26847</t>
+          <t>27476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19449</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>17222</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37629</t>
+          <t>40160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2935870</t>
+          <t>2931642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3016816</t>
+          <t>3014372</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3023544</t>
+          <t>3023939</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3106847</t>
+          <t>3105735</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5982168</t>
+          <t>5974510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6097573</t>
+          <t>6091875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,27%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>302005</t>
+          <t>303142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377670</t>
+          <t>378567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>329850</t>
+          <t>329338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>403335</t>
+          <t>406403</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>658119</t>
+          <t>662225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>763547</t>
+          <t>768399</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59838</t>
+          <t>60579</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99160</t>
+          <t>98171</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56359</t>
+          <t>56355</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>94237</t>
+          <t>91983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>128670</t>
+          <t>127174</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>180418</t>
+          <t>179080</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>629074</t>
+          <t>627504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>664609</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>806515</t>
+          <t>805963</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>854859</t>
+          <t>854720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1452829</t>
+          <t>1449171</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1514052</t>
+          <t>1510751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59701</t>
+          <t>58732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90577</t>
+          <t>90428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93448</t>
+          <t>93849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137029</t>
+          <t>138024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160891</t>
+          <t>161004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214161</t>
+          <t>214185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17236</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39540</t>
+          <t>39455</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>27063</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54703</t>
+          <t>54082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49421</t>
+          <t>52376</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83309</t>
+          <t>84551</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1708155</t>
+          <t>1711002</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1777229</t>
+          <t>1776340</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1611293</t>
+          <t>1611064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1679162</t>
+          <t>1676588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3346310</t>
+          <t>3344331</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3440141</t>
+          <t>3437270</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>224233</t>
+          <t>225648</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>287352</t>
+          <t>285843</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>221228</t>
+          <t>220008</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>281901</t>
+          <t>280267</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>457934</t>
+          <t>460995</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>544729</t>
+          <t>546590</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48376</t>
+          <t>48813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80742</t>
+          <t>82693</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,47 +5540,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>77163</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>61387</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>96603</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>3,91%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>77163</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>59713</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>95515</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116858</t>
+          <t>119994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164042</t>
+          <t>165453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>424080</t>
+          <t>426087</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>461734</t>
+          <t>463452</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>433617</t>
+          <t>433906</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>469617</t>
+          <t>471275</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>871707</t>
+          <t>871230</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>924012</t>
+          <t>922507</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59882</t>
+          <t>58783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94836</t>
+          <t>93226</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55147</t>
+          <t>56130</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88317</t>
+          <t>89056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123954</t>
+          <t>123748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168055</t>
+          <t>168229</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31260</t>
+          <t>30026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30913</t>
+          <t>30654</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26974</t>
+          <t>27646</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52735</t>
+          <t>55522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2792523</t>
+          <t>2793386</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2879354</t>
+          <t>2882468</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2886148</t>
+          <t>2888654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2977881</t>
+          <t>2972850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5713574</t>
+          <t>5703926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5833250</t>
+          <t>5826534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,04%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364580</t>
+          <t>365176</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>443000</t>
+          <t>440703</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>392915</t>
+          <t>392728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>478849</t>
+          <t>473445</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>779443</t>
+          <t>784346</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>888987</t>
+          <t>895692</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88670</t>
+          <t>90541</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>132185</t>
+          <t>133048</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>113956</t>
+          <t>116104</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>161536</t>
+          <t>160584</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>216089</t>
+          <t>216307</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>279842</t>
+          <t>280879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>465502</t>
+          <t>520642</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>452750</t>
+          <t>504572</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>475933</t>
+          <t>533479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>669380</t>
+          <t>726917</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>655528</t>
+          <t>711222</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>681361</t>
+          <t>740084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1134882</t>
+          <t>1247559</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1117664</t>
+          <t>1225754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1151348</t>
+          <t>1266113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>50229</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58381</t>
+          <t>64064</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47689</t>
+          <t>52671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72373</t>
+          <t>78654</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>87582</t>
+          <t>100688</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73105</t>
+          <t>84958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103334</t>
+          <t>120147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15672</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9533</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26038</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22101</t>
+          <t>26127</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,17 +7189,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>31564</t>
+          <t>34908</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23543</t>
+          <t>25234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42893</t>
+          <t>46458</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>510376</t>
+          <t>573935</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>510376</t>
+          <t>573935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>510376</t>
+          <t>573935</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>743653</t>
+          <t>809220</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>743653</t>
+          <t>809220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>743653</t>
+          <t>809220</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1254029</t>
+          <t>1383155</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1254029</t>
+          <t>1383155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1254029</t>
+          <t>1383155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2113503</t>
+          <t>2035802</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2076547</t>
+          <t>2004497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2168237</t>
+          <t>2064717</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2060135</t>
+          <t>1967622</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2028598</t>
+          <t>1939642</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2109602</t>
+          <t>1991314</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4173638</t>
+          <t>4003424</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4122569</t>
+          <t>3963132</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4239346</t>
+          <t>4039436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>138797</t>
+          <t>156451</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95566</t>
+          <t>131182</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>170979</t>
+          <t>184957</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>134307</t>
+          <t>154470</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96813</t>
+          <t>133276</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>162909</t>
+          <t>180443</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>273103</t>
+          <t>310921</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>218423</t>
+          <t>278983</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>316798</t>
+          <t>347039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28818</t>
+          <t>29594</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>17930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48834</t>
+          <t>45903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37569</t>
+          <t>39897</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25247</t>
+          <t>29150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52440</t>
+          <t>54336</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,27 +7645,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>66387</t>
+          <t>69491</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48201</t>
+          <t>52565</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92651</t>
+          <t>89754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2281117</t>
+          <t>2221846</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2281117</t>
+          <t>2221846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2281117</t>
+          <t>2221846</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2232011</t>
+          <t>2161990</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2232011</t>
+          <t>2161990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2232011</t>
+          <t>2161990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4513128</t>
+          <t>4383836</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4513128</t>
+          <t>4383836</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4513128</t>
+          <t>4383836</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>572229</t>
+          <t>630934</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>553850</t>
+          <t>611065</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>587568</t>
+          <t>647575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>571353</t>
+          <t>636037</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>555445</t>
+          <t>617955</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>584543</t>
+          <t>650197</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1143582</t>
+          <t>1266971</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1118569</t>
+          <t>1241572</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1165146</t>
+          <t>1289616</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52577</t>
+          <t>56721</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>43576</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68963</t>
+          <t>74112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64886</t>
+          <t>69107</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53718</t>
+          <t>56714</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80121</t>
+          <t>85521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>117463</t>
+          <t>125828</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98933</t>
+          <t>106302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138147</t>
+          <t>148476</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19250</t>
+          <t>21263</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>13440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30121</t>
+          <t>34002</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>15748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29338</t>
+          <t>32179</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>39320</t>
+          <t>44369</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28239</t>
+          <t>33027</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52582</t>
+          <t>60754</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>644056</t>
+          <t>708918</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>644056</t>
+          <t>708918</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>644056</t>
+          <t>708918</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>656309</t>
+          <t>728249</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>656309</t>
+          <t>728249</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>656309</t>
+          <t>728249</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1300365</t>
+          <t>1437167</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1300365</t>
+          <t>1437167</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1300365</t>
+          <t>1437167</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3151234</t>
+          <t>3187378</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3107834</t>
+          <t>3147449</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3214570</t>
+          <t>3224132</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3300868</t>
+          <t>3330576</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3260740</t>
+          <t>3296550</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3364211</t>
+          <t>3362652</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6452103</t>
+          <t>6517954</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6392597</t>
+          <t>6460965</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6538881</t>
+          <t>6564702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>220576</t>
+          <t>249796</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173293</t>
+          <t>217070</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>256734</t>
+          <t>286711</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>257573</t>
+          <t>287641</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209987</t>
+          <t>260122</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>290877</t>
+          <t>317592</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>478149</t>
+          <t>537436</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407039</t>
+          <t>497973</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>527957</t>
+          <t>584725</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>63740</t>
+          <t>67526</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44159</t>
+          <t>51535</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>86121</t>
+          <t>89287</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73532</t>
+          <t>81242</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57725</t>
+          <t>66017</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91995</t>
+          <t>99476</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>137272</t>
+          <t>148768</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114172</t>
+          <t>126123</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>164476</t>
+          <t>176985</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3435550</t>
+          <t>3504700</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3435550</t>
+          <t>3504700</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3435550</t>
+          <t>3504700</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3631973</t>
+          <t>3699458</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3631973</t>
+          <t>3699458</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3631973</t>
+          <t>3699458</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7067523</t>
+          <t>7204158</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7067523</t>
+          <t>7204158</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7067523</t>
+          <t>7204158</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
